--- a/Output/MASTER.xlsx
+++ b/Output/MASTER.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH217"/>
+  <dimension ref="A1:AI217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,6 +585,11 @@
       <c r="AH1" t="inlineStr">
         <is>
           <t>TRADED_VAL</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Delivery %</t>
         </is>
       </c>
     </row>
@@ -665,6 +670,7 @@
       <c r="AH2" t="n">
         <v>185977655</v>
       </c>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -743,6 +749,7 @@
       <c r="AH3" t="n">
         <v>34383773094</v>
       </c>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -821,6 +828,7 @@
       <c r="AH4" t="n">
         <v>262322310</v>
       </c>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -944,6 +952,9 @@
       </c>
       <c r="AH5" t="n">
         <v>4203212600</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>47.66</v>
       </c>
     </row>
     <row r="6">
@@ -1023,6 +1034,7 @@
       <c r="AH6" t="n">
         <v>58021224969.5</v>
       </c>
+      <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1101,6 +1113,7 @@
       <c r="AH7" t="n">
         <v>3502266930</v>
       </c>
+      <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1225,6 +1238,9 @@
       <c r="AH8" t="n">
         <v>5324034650</v>
       </c>
+      <c r="AI8" t="n">
+        <v>44.16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1349,6 +1365,9 @@
       <c r="AH9" t="n">
         <v>1164846815</v>
       </c>
+      <c r="AI9" t="n">
+        <v>60.79</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1473,6 +1492,9 @@
       <c r="AH10" t="n">
         <v>2020258700</v>
       </c>
+      <c r="AI10" t="n">
+        <v>55.07</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1597,6 +1619,9 @@
       <c r="AH11" t="n">
         <v>3354512730</v>
       </c>
+      <c r="AI11" t="n">
+        <v>43.79</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1721,6 +1746,9 @@
       <c r="AH12" t="n">
         <v>1140096308</v>
       </c>
+      <c r="AI12" t="n">
+        <v>47.25</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1845,6 +1873,9 @@
       <c r="AH13" t="n">
         <v>705816450</v>
       </c>
+      <c r="AI13" t="n">
+        <v>39.05</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1969,6 +2000,9 @@
       <c r="AH14" t="n">
         <v>1186982257.5</v>
       </c>
+      <c r="AI14" t="n">
+        <v>65.16</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2093,6 +2127,9 @@
       <c r="AH15" t="n">
         <v>17666523650</v>
       </c>
+      <c r="AI15" t="n">
+        <v>46.85</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2217,6 +2254,9 @@
       <c r="AH16" t="n">
         <v>3170851560</v>
       </c>
+      <c r="AI16" t="n">
+        <v>49.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2341,6 +2381,9 @@
       <c r="AH17" t="n">
         <v>497374115</v>
       </c>
+      <c r="AI17" t="n">
+        <v>71.15000000000001</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2465,6 +2508,9 @@
       <c r="AH18" t="n">
         <v>2196083010</v>
       </c>
+      <c r="AI18" t="n">
+        <v>60.05</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2589,6 +2635,9 @@
       <c r="AH19" t="n">
         <v>4060968250</v>
       </c>
+      <c r="AI19" t="n">
+        <v>58.91</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2713,6 +2762,9 @@
       <c r="AH20" t="n">
         <v>2321056750</v>
       </c>
+      <c r="AI20" t="n">
+        <v>58.14</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2837,6 +2889,9 @@
       <c r="AH21" t="n">
         <v>2977348447.5</v>
       </c>
+      <c r="AI21" t="n">
+        <v>41.82</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2961,6 +3016,9 @@
       <c r="AH22" t="n">
         <v>7038010740</v>
       </c>
+      <c r="AI22" t="n">
+        <v>63.9</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3085,6 +3143,9 @@
       <c r="AH23" t="n">
         <v>596790500</v>
       </c>
+      <c r="AI23" t="n">
+        <v>52.46</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3209,6 +3270,9 @@
       <c r="AH24" t="n">
         <v>487153192.5</v>
       </c>
+      <c r="AI24" t="n">
+        <v>71.2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3333,6 +3397,9 @@
       <c r="AH25" t="n">
         <v>1137379740</v>
       </c>
+      <c r="AI25" t="n">
+        <v>51.49</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3457,6 +3524,9 @@
       <c r="AH26" t="n">
         <v>1707706271.25</v>
       </c>
+      <c r="AI26" t="n">
+        <v>57.88</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3581,6 +3651,9 @@
       <c r="AH27" t="n">
         <v>8210576840</v>
       </c>
+      <c r="AI27" t="n">
+        <v>62.72</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3705,6 +3778,9 @@
       <c r="AH28" t="n">
         <v>2830101813.75</v>
       </c>
+      <c r="AI28" t="n">
+        <v>39.75</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3829,6 +3905,9 @@
       <c r="AH29" t="n">
         <v>4129542388</v>
       </c>
+      <c r="AI29" t="n">
+        <v>51.42</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3953,6 +4032,9 @@
       <c r="AH30" t="n">
         <v>3422531250</v>
       </c>
+      <c r="AI30" t="n">
+        <v>50.96</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4077,6 +4159,9 @@
       <c r="AH31" t="n">
         <v>2000944012.5</v>
       </c>
+      <c r="AI31" t="n">
+        <v>36.18</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4201,6 +4286,9 @@
       <c r="AH32" t="n">
         <v>4741735710</v>
       </c>
+      <c r="AI32" t="n">
+        <v>61.9</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4325,6 +4413,9 @@
       <c r="AH33" t="n">
         <v>2126831460</v>
       </c>
+      <c r="AI33" t="n">
+        <v>53.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4449,6 +4540,9 @@
       <c r="AH34" t="n">
         <v>1144081360</v>
       </c>
+      <c r="AI34" t="n">
+        <v>59.88</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4573,6 +4667,9 @@
       <c r="AH35" t="n">
         <v>1429724400</v>
       </c>
+      <c r="AI35" t="n">
+        <v>66.42</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4697,6 +4794,9 @@
       <c r="AH36" t="n">
         <v>11247784600</v>
       </c>
+      <c r="AI36" t="n">
+        <v>54.12</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4821,6 +4921,9 @@
       <c r="AH37" t="n">
         <v>2481461225</v>
       </c>
+      <c r="AI37" t="n">
+        <v>39.53</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4945,6 +5048,9 @@
       <c r="AH38" t="n">
         <v>2585723500</v>
       </c>
+      <c r="AI38" t="n">
+        <v>55.05</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5069,6 +5175,9 @@
       <c r="AH39" t="n">
         <v>2129130008.5</v>
       </c>
+      <c r="AI39" t="n">
+        <v>47.43</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5193,6 +5302,9 @@
       <c r="AH40" t="n">
         <v>3147637235</v>
       </c>
+      <c r="AI40" t="n">
+        <v>36.28</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5317,6 +5429,9 @@
       <c r="AH41" t="n">
         <v>3500475900</v>
       </c>
+      <c r="AI41" t="n">
+        <v>57.19</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5441,6 +5556,9 @@
       <c r="AH42" t="n">
         <v>6960696312.5</v>
       </c>
+      <c r="AI42" t="n">
+        <v>66.23999999999999</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5565,6 +5683,9 @@
       <c r="AH43" t="n">
         <v>14132534916.25</v>
       </c>
+      <c r="AI43" t="n">
+        <v>56.99</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5689,6 +5810,9 @@
       <c r="AH44" t="n">
         <v>5092166400</v>
       </c>
+      <c r="AI44" t="n">
+        <v>46.97</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5813,6 +5937,9 @@
       <c r="AH45" t="n">
         <v>2147510323</v>
       </c>
+      <c r="AI45" t="n">
+        <v>50.65</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5937,6 +6064,9 @@
       <c r="AH46" t="n">
         <v>7165134312</v>
       </c>
+      <c r="AI46" t="n">
+        <v>28.18</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6061,6 +6191,9 @@
       <c r="AH47" t="n">
         <v>1625644250</v>
       </c>
+      <c r="AI47" t="n">
+        <v>62.92</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6185,6 +6318,9 @@
       <c r="AH48" t="n">
         <v>2285835700</v>
       </c>
+      <c r="AI48" t="n">
+        <v>43.81</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6309,6 +6445,9 @@
       <c r="AH49" t="n">
         <v>5658048687.5</v>
       </c>
+      <c r="AI49" t="n">
+        <v>45.73</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6433,6 +6572,9 @@
       <c r="AH50" t="n">
         <v>1729987078.75</v>
       </c>
+      <c r="AI50" t="n">
+        <v>53.84</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6557,6 +6699,9 @@
       <c r="AH51" t="n">
         <v>5497370900</v>
       </c>
+      <c r="AI51" t="n">
+        <v>60.68</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6681,6 +6826,9 @@
       <c r="AH52" t="n">
         <v>2511243210</v>
       </c>
+      <c r="AI52" t="n">
+        <v>51.38</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6805,6 +6953,9 @@
       <c r="AH53" t="n">
         <v>2904599350</v>
       </c>
+      <c r="AI53" t="n">
+        <v>52.09</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6929,6 +7080,9 @@
       <c r="AH54" t="n">
         <v>6164720145</v>
       </c>
+      <c r="AI54" t="n">
+        <v>58.17</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7053,6 +7207,9 @@
       <c r="AH55" t="n">
         <v>1845923050</v>
       </c>
+      <c r="AI55" t="n">
+        <v>56.59</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7177,6 +7334,9 @@
       <c r="AH56" t="n">
         <v>1070256167.25</v>
       </c>
+      <c r="AI56" t="n">
+        <v>70.34999999999999</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7301,6 +7461,9 @@
       <c r="AH57" t="n">
         <v>2643306412.5</v>
       </c>
+      <c r="AI57" t="n">
+        <v>50.09</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7425,6 +7588,9 @@
       <c r="AH58" t="n">
         <v>1359453100</v>
       </c>
+      <c r="AI58" t="n">
+        <v>68.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7549,6 +7715,9 @@
       <c r="AH59" t="n">
         <v>1107883878.75</v>
       </c>
+      <c r="AI59" t="n">
+        <v>60.28</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7673,6 +7842,9 @@
       <c r="AH60" t="n">
         <v>617947165</v>
       </c>
+      <c r="AI60" t="n">
+        <v>46.36</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7797,6 +7969,9 @@
       <c r="AH61" t="n">
         <v>1986182650</v>
       </c>
+      <c r="AI61" t="n">
+        <v>43.98</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7921,6 +8096,9 @@
       <c r="AH62" t="n">
         <v>1961243057.25</v>
       </c>
+      <c r="AI62" t="n">
+        <v>48.17</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8045,6 +8223,9 @@
       <c r="AH63" t="n">
         <v>3359805637.5</v>
       </c>
+      <c r="AI63" t="n">
+        <v>48.1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8169,6 +8350,9 @@
       <c r="AH64" t="n">
         <v>2493470870</v>
       </c>
+      <c r="AI64" t="n">
+        <v>55.53</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8293,6 +8477,9 @@
       <c r="AH65" t="n">
         <v>1207506458.75</v>
       </c>
+      <c r="AI65" t="n">
+        <v>64.14</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8417,6 +8604,9 @@
       <c r="AH66" t="n">
         <v>5233770780</v>
       </c>
+      <c r="AI66" t="n">
+        <v>47.32</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8541,6 +8731,9 @@
       <c r="AH67" t="n">
         <v>2672572108.5</v>
       </c>
+      <c r="AI67" t="n">
+        <v>47.53</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8665,6 +8858,9 @@
       <c r="AH68" t="n">
         <v>6893951625</v>
       </c>
+      <c r="AI68" t="n">
+        <v>57.73</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8789,6 +8985,9 @@
       <c r="AH69" t="n">
         <v>10189452950</v>
       </c>
+      <c r="AI69" t="n">
+        <v>55.46</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8913,6 +9112,9 @@
       <c r="AH70" t="n">
         <v>1434559665</v>
       </c>
+      <c r="AI70" t="n">
+        <v>46.68</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9037,6 +9239,9 @@
       <c r="AH71" t="n">
         <v>12877315457.5</v>
       </c>
+      <c r="AI71" t="n">
+        <v>60.53</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9161,6 +9366,9 @@
       <c r="AH72" t="n">
         <v>689402325</v>
       </c>
+      <c r="AI72" t="n">
+        <v>56.71</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9285,6 +9493,9 @@
       <c r="AH73" t="n">
         <v>1369666540</v>
       </c>
+      <c r="AI73" t="n">
+        <v>45.14</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9409,6 +9620,9 @@
       <c r="AH74" t="n">
         <v>2432275760</v>
       </c>
+      <c r="AI74" t="n">
+        <v>43.3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9533,6 +9747,9 @@
       <c r="AH75" t="n">
         <v>8204155646.25</v>
       </c>
+      <c r="AI75" t="n">
+        <v>57.74</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9657,6 +9874,9 @@
       <c r="AH76" t="n">
         <v>997717170</v>
       </c>
+      <c r="AI76" t="n">
+        <v>60.44</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9781,6 +10001,9 @@
       <c r="AH77" t="n">
         <v>694061187.5</v>
       </c>
+      <c r="AI77" t="n">
+        <v>60.42</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9905,6 +10128,9 @@
       <c r="AH78" t="n">
         <v>1409833650</v>
       </c>
+      <c r="AI78" t="n">
+        <v>35.7</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10029,6 +10255,9 @@
       <c r="AH79" t="n">
         <v>4582183970</v>
       </c>
+      <c r="AI79" t="n">
+        <v>64.31</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10153,6 +10382,9 @@
       <c r="AH80" t="n">
         <v>2920379560</v>
       </c>
+      <c r="AI80" t="n">
+        <v>40.94</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10277,6 +10509,9 @@
       <c r="AH81" t="n">
         <v>1365458600</v>
       </c>
+      <c r="AI81" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10401,6 +10636,9 @@
       <c r="AH82" t="n">
         <v>6448450905</v>
       </c>
+      <c r="AI82" t="n">
+        <v>49.07</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10525,6 +10763,9 @@
       <c r="AH83" t="n">
         <v>2969194830</v>
       </c>
+      <c r="AI83" t="n">
+        <v>68.34</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10649,6 +10890,9 @@
       <c r="AH84" t="n">
         <v>1118495125</v>
       </c>
+      <c r="AI84" t="n">
+        <v>48.92</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10773,6 +11017,9 @@
       <c r="AH85" t="n">
         <v>3165822180</v>
       </c>
+      <c r="AI85" t="n">
+        <v>51.59</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10897,6 +11144,9 @@
       <c r="AH86" t="n">
         <v>4631562930</v>
       </c>
+      <c r="AI86" t="n">
+        <v>52.12</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11021,6 +11271,9 @@
       <c r="AH87" t="n">
         <v>2821476915</v>
       </c>
+      <c r="AI87" t="n">
+        <v>58.7</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11145,6 +11398,9 @@
       <c r="AH88" t="n">
         <v>2127340935</v>
       </c>
+      <c r="AI88" t="n">
+        <v>46.98</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11269,6 +11525,9 @@
       <c r="AH89" t="n">
         <v>8886739890</v>
       </c>
+      <c r="AI89" t="n">
+        <v>48.61</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11393,6 +11652,9 @@
       <c r="AH90" t="n">
         <v>1416843900</v>
       </c>
+      <c r="AI90" t="n">
+        <v>53.24</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11517,6 +11779,9 @@
       <c r="AH91" t="n">
         <v>1119679837.5</v>
       </c>
+      <c r="AI91" t="n">
+        <v>50.67</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11641,6 +11906,9 @@
       <c r="AH92" t="n">
         <v>549399700</v>
       </c>
+      <c r="AI92" t="n">
+        <v>39.37</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11765,6 +12033,9 @@
       <c r="AH93" t="n">
         <v>1158048360</v>
       </c>
+      <c r="AI93" t="n">
+        <v>54.87</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11889,6 +12160,9 @@
       <c r="AH94" t="n">
         <v>779624755</v>
       </c>
+      <c r="AI94" t="n">
+        <v>57.47</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -12013,6 +12287,9 @@
       <c r="AH95" t="n">
         <v>2201703997.5</v>
       </c>
+      <c r="AI95" t="n">
+        <v>52.77</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -12137,6 +12414,9 @@
       <c r="AH96" t="n">
         <v>4203998010</v>
       </c>
+      <c r="AI96" t="n">
+        <v>48.15</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12261,6 +12541,9 @@
       <c r="AH97" t="n">
         <v>5779217675</v>
       </c>
+      <c r="AI97" t="n">
+        <v>44.47</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12385,6 +12668,9 @@
       <c r="AH98" t="n">
         <v>1966744920</v>
       </c>
+      <c r="AI98" t="n">
+        <v>65.14</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12509,6 +12795,9 @@
       <c r="AH99" t="n">
         <v>453534668.75</v>
       </c>
+      <c r="AI99" t="n">
+        <v>61.08</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12633,6 +12922,9 @@
       <c r="AH100" t="n">
         <v>1072426990.5</v>
       </c>
+      <c r="AI100" t="n">
+        <v>51.93</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12757,6 +13049,9 @@
       <c r="AH101" t="n">
         <v>722303353</v>
       </c>
+      <c r="AI101" t="n">
+        <v>46.82</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12881,6 +13176,9 @@
       <c r="AH102" t="n">
         <v>2105167687.5</v>
       </c>
+      <c r="AI102" t="n">
+        <v>39.55</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -13005,6 +13303,9 @@
       <c r="AH103" t="n">
         <v>927619160</v>
       </c>
+      <c r="AI103" t="n">
+        <v>41.6</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -13129,6 +13430,9 @@
       <c r="AH104" t="n">
         <v>2382855375</v>
       </c>
+      <c r="AI104" t="n">
+        <v>61.23</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -13253,6 +13557,9 @@
       <c r="AH105" t="n">
         <v>8737368096.25</v>
       </c>
+      <c r="AI105" t="n">
+        <v>32.1</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13377,6 +13684,9 @@
       <c r="AH106" t="n">
         <v>1248834380</v>
       </c>
+      <c r="AI106" t="n">
+        <v>42.18</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -13501,6 +13811,9 @@
       <c r="AH107" t="n">
         <v>3074023205</v>
       </c>
+      <c r="AI107" t="n">
+        <v>56.17</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -13625,6 +13938,9 @@
       <c r="AH108" t="n">
         <v>7837799025</v>
       </c>
+      <c r="AI108" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -13749,6 +14065,9 @@
       <c r="AH109" t="n">
         <v>8586603500</v>
       </c>
+      <c r="AI109" t="n">
+        <v>50.37</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -13873,6 +14192,9 @@
       <c r="AH110" t="n">
         <v>1220540812.5</v>
       </c>
+      <c r="AI110" t="n">
+        <v>65.28</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13997,6 +14319,9 @@
       <c r="AH111" t="n">
         <v>2406363855</v>
       </c>
+      <c r="AI111" t="n">
+        <v>59.59</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -14121,6 +14446,9 @@
       <c r="AH112" t="n">
         <v>809371500</v>
       </c>
+      <c r="AI112" t="n">
+        <v>64.89</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -14245,6 +14573,9 @@
       <c r="AH113" t="n">
         <v>2443144477.5</v>
       </c>
+      <c r="AI113" t="n">
+        <v>49.85</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -14369,6 +14700,9 @@
       <c r="AH114" t="n">
         <v>1646072463</v>
       </c>
+      <c r="AI114" t="n">
+        <v>61.41</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -14493,6 +14827,9 @@
       <c r="AH115" t="n">
         <v>1355013817.5</v>
       </c>
+      <c r="AI115" t="n">
+        <v>56.49</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -14617,6 +14954,9 @@
       <c r="AH116" t="n">
         <v>1673890650</v>
       </c>
+      <c r="AI116" t="n">
+        <v>53.25</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -14741,6 +15081,9 @@
       <c r="AH117" t="n">
         <v>11688403350</v>
       </c>
+      <c r="AI117" t="n">
+        <v>47.63</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14865,6 +15208,9 @@
       <c r="AH118" t="n">
         <v>1268029350</v>
       </c>
+      <c r="AI118" t="n">
+        <v>68.89</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -14989,6 +15335,9 @@
       <c r="AH119" t="n">
         <v>3149619875</v>
       </c>
+      <c r="AI119" t="n">
+        <v>60.8</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -15113,6 +15462,9 @@
       <c r="AH120" t="n">
         <v>1137738778.75</v>
       </c>
+      <c r="AI120" t="n">
+        <v>51.01</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -15237,6 +15589,9 @@
       <c r="AH121" t="n">
         <v>4186898677.5</v>
       </c>
+      <c r="AI121" t="n">
+        <v>63.3</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -15361,6 +15716,9 @@
       <c r="AH122" t="n">
         <v>1090908245</v>
       </c>
+      <c r="AI122" t="n">
+        <v>49.5</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -15485,6 +15843,9 @@
       <c r="AH123" t="n">
         <v>1012200120</v>
       </c>
+      <c r="AI123" t="n">
+        <v>53.61</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -15609,6 +15970,9 @@
       <c r="AH124" t="n">
         <v>1409769843.75</v>
       </c>
+      <c r="AI124" t="n">
+        <v>59.92</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15733,6 +16097,9 @@
       <c r="AH125" t="n">
         <v>2962473962.5</v>
       </c>
+      <c r="AI125" t="n">
+        <v>49.74</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -15857,6 +16224,9 @@
       <c r="AH126" t="n">
         <v>2017970687.5</v>
       </c>
+      <c r="AI126" t="n">
+        <v>62.33</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -15981,6 +16351,9 @@
       <c r="AH127" t="n">
         <v>1301936080</v>
       </c>
+      <c r="AI127" t="n">
+        <v>45.86</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -16105,6 +16478,9 @@
       <c r="AH128" t="n">
         <v>1274458987.5</v>
       </c>
+      <c r="AI128" t="n">
+        <v>57.93</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -16229,6 +16605,9 @@
       <c r="AH129" t="n">
         <v>2099997295</v>
       </c>
+      <c r="AI129" t="n">
+        <v>54.11</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -16353,6 +16732,9 @@
       <c r="AH130" t="n">
         <v>2515406520</v>
       </c>
+      <c r="AI130" t="n">
+        <v>56.49</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -16477,6 +16859,9 @@
       <c r="AH131" t="n">
         <v>15335523787.5</v>
       </c>
+      <c r="AI131" t="n">
+        <v>56.25</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -16601,6 +16986,9 @@
       <c r="AH132" t="n">
         <v>16118483802</v>
       </c>
+      <c r="AI132" t="n">
+        <v>48.06</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -16725,6 +17113,9 @@
       <c r="AH133" t="n">
         <v>626605575</v>
       </c>
+      <c r="AI133" t="n">
+        <v>53.15</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -16849,6 +17240,9 @@
       <c r="AH134" t="n">
         <v>1165588530</v>
       </c>
+      <c r="AI134" t="n">
+        <v>41.38</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -16973,6 +17367,9 @@
       <c r="AH135" t="n">
         <v>345180721.5</v>
       </c>
+      <c r="AI135" t="n">
+        <v>41.76</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -17097,6 +17494,9 @@
       <c r="AH136" t="n">
         <v>1120996500</v>
       </c>
+      <c r="AI136" t="n">
+        <v>62.62</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -17221,6 +17621,9 @@
       <c r="AH137" t="n">
         <v>616602675</v>
       </c>
+      <c r="AI137" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -17345,6 +17748,9 @@
       <c r="AH138" t="n">
         <v>2825960250</v>
       </c>
+      <c r="AI138" t="n">
+        <v>40.5</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -17469,6 +17875,9 @@
       <c r="AH139" t="n">
         <v>835209600</v>
       </c>
+      <c r="AI139" t="n">
+        <v>33.56</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -17593,6 +18002,9 @@
       <c r="AH140" t="n">
         <v>1590367750</v>
       </c>
+      <c r="AI140" t="n">
+        <v>26.29</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -17717,6 +18129,9 @@
       <c r="AH141" t="n">
         <v>1788050737.5</v>
       </c>
+      <c r="AI141" t="n">
+        <v>41.2</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -17841,6 +18256,9 @@
       <c r="AH142" t="n">
         <v>639466187.5</v>
       </c>
+      <c r="AI142" t="n">
+        <v>55.1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -17965,6 +18383,9 @@
       <c r="AH143" t="n">
         <v>2228854430</v>
       </c>
+      <c r="AI143" t="n">
+        <v>40.4</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -18089,6 +18510,9 @@
       <c r="AH144" t="n">
         <v>1455138945</v>
       </c>
+      <c r="AI144" t="n">
+        <v>63.33</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -18213,6 +18637,9 @@
       <c r="AH145" t="n">
         <v>1277402780</v>
       </c>
+      <c r="AI145" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -18337,6 +18764,9 @@
       <c r="AH146" t="n">
         <v>5078740350</v>
       </c>
+      <c r="AI146" t="n">
+        <v>57.23</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -18461,6 +18891,9 @@
       <c r="AH147" t="n">
         <v>5121738720</v>
       </c>
+      <c r="AI147" t="n">
+        <v>48.01</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -18585,6 +19018,9 @@
       <c r="AH148" t="n">
         <v>2173865731</v>
       </c>
+      <c r="AI148" t="n">
+        <v>44.37</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -18709,6 +19145,9 @@
       <c r="AH149" t="n">
         <v>1419123100</v>
       </c>
+      <c r="AI149" t="n">
+        <v>64.53</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -18833,6 +19272,9 @@
       <c r="AH150" t="n">
         <v>973889661.25</v>
       </c>
+      <c r="AI150" t="n">
+        <v>37.69</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -18957,6 +19399,9 @@
       <c r="AH151" t="n">
         <v>4254915300</v>
       </c>
+      <c r="AI151" t="n">
+        <v>47.23</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -19081,6 +19526,9 @@
       <c r="AH152" t="n">
         <v>3769828125</v>
       </c>
+      <c r="AI152" t="n">
+        <v>51.96</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -19205,6 +19653,9 @@
       <c r="AH153" t="n">
         <v>3456912557.5</v>
       </c>
+      <c r="AI153" t="n">
+        <v>39.21</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -19329,6 +19780,9 @@
       <c r="AH154" t="n">
         <v>2420226228</v>
       </c>
+      <c r="AI154" t="n">
+        <v>51.85</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -19453,6 +19907,9 @@
       <c r="AH155" t="n">
         <v>2677199925</v>
       </c>
+      <c r="AI155" t="n">
+        <v>60.22</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -19577,6 +20034,9 @@
       <c r="AH156" t="n">
         <v>1701052920</v>
       </c>
+      <c r="AI156" t="n">
+        <v>49.4</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -19701,6 +20161,9 @@
       <c r="AH157" t="n">
         <v>1110815828.75</v>
       </c>
+      <c r="AI157" t="n">
+        <v>50.04</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -19825,6 +20288,9 @@
       <c r="AH158" t="n">
         <v>2523410377.5</v>
       </c>
+      <c r="AI158" t="n">
+        <v>42.81</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -19949,6 +20415,9 @@
       <c r="AH159" t="n">
         <v>1740743070</v>
       </c>
+      <c r="AI159" t="n">
+        <v>41.78</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -20073,6 +20542,9 @@
       <c r="AH160" t="n">
         <v>1055705737.5</v>
       </c>
+      <c r="AI160" t="n">
+        <v>61.31</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -20197,6 +20669,9 @@
       <c r="AH161" t="n">
         <v>1290650097.5</v>
       </c>
+      <c r="AI161" t="n">
+        <v>39.88</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -20321,6 +20796,9 @@
       <c r="AH162" t="n">
         <v>2513038770</v>
       </c>
+      <c r="AI162" t="n">
+        <v>48.63</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -20445,6 +20923,9 @@
       <c r="AH163" t="n">
         <v>6297647975</v>
       </c>
+      <c r="AI163" t="n">
+        <v>45.7</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -20569,6 +21050,9 @@
       <c r="AH164" t="n">
         <v>2770583600</v>
       </c>
+      <c r="AI164" t="n">
+        <v>62.55</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -20693,6 +21177,9 @@
       <c r="AH165" t="n">
         <v>2338364125</v>
       </c>
+      <c r="AI165" t="n">
+        <v>40.34</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -20817,6 +21304,9 @@
       <c r="AH166" t="n">
         <v>2055346650</v>
       </c>
+      <c r="AI166" t="n">
+        <v>48.04</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -20941,6 +21431,9 @@
       <c r="AH167" t="n">
         <v>1123756612.5</v>
       </c>
+      <c r="AI167" t="n">
+        <v>49.84</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -21065,6 +21558,9 @@
       <c r="AH168" t="n">
         <v>1767159250</v>
       </c>
+      <c r="AI168" t="n">
+        <v>52.17</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -21189,6 +21685,9 @@
       <c r="AH169" t="n">
         <v>4015520955</v>
       </c>
+      <c r="AI169" t="n">
+        <v>52.09</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -21313,6 +21812,9 @@
       <c r="AH170" t="n">
         <v>2509544475</v>
       </c>
+      <c r="AI170" t="n">
+        <v>53.81</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -21437,6 +21939,9 @@
       <c r="AH171" t="n">
         <v>2517365867.5</v>
       </c>
+      <c r="AI171" t="n">
+        <v>62.51</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -21561,6 +22066,9 @@
       <c r="AH172" t="n">
         <v>1106176850</v>
       </c>
+      <c r="AI172" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -21685,6 +22193,9 @@
       <c r="AH173" t="n">
         <v>4802886768.75</v>
       </c>
+      <c r="AI173" t="n">
+        <v>50.98</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -21809,6 +22320,9 @@
       <c r="AH174" t="n">
         <v>547587293.75</v>
       </c>
+      <c r="AI174" t="n">
+        <v>39.86</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -21933,6 +22447,9 @@
       <c r="AH175" t="n">
         <v>714527835</v>
       </c>
+      <c r="AI175" t="n">
+        <v>52.89</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -22057,6 +22574,9 @@
       <c r="AH176" t="n">
         <v>918704023.5</v>
       </c>
+      <c r="AI176" t="n">
+        <v>56.16</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -22181,6 +22701,9 @@
       <c r="AH177" t="n">
         <v>1002463137.5</v>
       </c>
+      <c r="AI177" t="n">
+        <v>56.23</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -22305,6 +22828,9 @@
       <c r="AH178" t="n">
         <v>910231875</v>
       </c>
+      <c r="AI178" t="n">
+        <v>55.02</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -22429,6 +22955,9 @@
       <c r="AH179" t="n">
         <v>1240555790</v>
       </c>
+      <c r="AI179" t="n">
+        <v>56.28</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -22553,6 +23082,9 @@
       <c r="AH180" t="n">
         <v>6371213640</v>
       </c>
+      <c r="AI180" t="n">
+        <v>41.96</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -22677,6 +23209,9 @@
       <c r="AH181" t="n">
         <v>607738496.25</v>
       </c>
+      <c r="AI181" t="n">
+        <v>28.35</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -22801,6 +23336,9 @@
       <c r="AH182" t="n">
         <v>1565310425</v>
       </c>
+      <c r="AI182" t="n">
+        <v>42.8</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -22925,6 +23463,9 @@
       <c r="AH183" t="n">
         <v>9520787947.5</v>
       </c>
+      <c r="AI183" t="n">
+        <v>55.33</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -23049,6 +23590,9 @@
       <c r="AH184" t="n">
         <v>3950547900</v>
       </c>
+      <c r="AI184" t="n">
+        <v>48.89</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -23173,6 +23717,9 @@
       <c r="AH185" t="n">
         <v>448207662.5</v>
       </c>
+      <c r="AI185" t="n">
+        <v>39.09</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -23297,6 +23844,9 @@
       <c r="AH186" t="n">
         <v>5166472240</v>
       </c>
+      <c r="AI186" t="n">
+        <v>46.89</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -23421,6 +23971,9 @@
       <c r="AH187" t="n">
         <v>6554395956</v>
       </c>
+      <c r="AI187" t="n">
+        <v>33.78</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -23545,6 +24098,9 @@
       <c r="AH188" t="n">
         <v>1870114282.5</v>
       </c>
+      <c r="AI188" t="n">
+        <v>43.41</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -23669,6 +24225,9 @@
       <c r="AH189" t="n">
         <v>1542553645</v>
       </c>
+      <c r="AI189" t="n">
+        <v>47.14</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -23793,6 +24352,9 @@
       <c r="AH190" t="n">
         <v>873598060</v>
       </c>
+      <c r="AI190" t="n">
+        <v>45.96</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -23917,6 +24479,9 @@
       <c r="AH191" t="n">
         <v>1208176125</v>
       </c>
+      <c r="AI191" t="n">
+        <v>61.36</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -24041,6 +24606,9 @@
       <c r="AH192" t="n">
         <v>422660590</v>
       </c>
+      <c r="AI192" t="n">
+        <v>37.86</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -24165,6 +24733,9 @@
       <c r="AH193" t="n">
         <v>4703352080</v>
       </c>
+      <c r="AI193" t="n">
+        <v>43.06</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -24289,6 +24860,9 @@
       <c r="AH194" t="n">
         <v>2040472262.5</v>
       </c>
+      <c r="AI194" t="n">
+        <v>37.16</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -24413,6 +24987,9 @@
       <c r="AH195" t="n">
         <v>2948486300</v>
       </c>
+      <c r="AI195" t="n">
+        <v>42.44</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -24537,6 +25114,9 @@
       <c r="AH196" t="n">
         <v>854213160</v>
       </c>
+      <c r="AI196" t="n">
+        <v>46.02</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -24661,6 +25241,9 @@
       <c r="AH197" t="n">
         <v>7554480420</v>
       </c>
+      <c r="AI197" t="n">
+        <v>48.83</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -24785,6 +25368,9 @@
       <c r="AH198" t="n">
         <v>2008097100</v>
       </c>
+      <c r="AI198" t="n">
+        <v>33.58</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -24909,6 +25495,9 @@
       <c r="AH199" t="n">
         <v>5144791937.5</v>
       </c>
+      <c r="AI199" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -25033,6 +25622,9 @@
       <c r="AH200" t="n">
         <v>2324074005</v>
       </c>
+      <c r="AI200" t="n">
+        <v>49.78</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -25157,6 +25749,9 @@
       <c r="AH201" t="n">
         <v>2574413610</v>
       </c>
+      <c r="AI201" t="n">
+        <v>29.56</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -25281,6 +25876,9 @@
       <c r="AH202" t="n">
         <v>1097308590</v>
       </c>
+      <c r="AI202" t="n">
+        <v>40.44</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -25405,6 +26003,9 @@
       <c r="AH203" t="n">
         <v>989524182.5</v>
       </c>
+      <c r="AI203" t="n">
+        <v>58.72</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -25529,6 +26130,9 @@
       <c r="AH204" t="n">
         <v>3222438300</v>
       </c>
+      <c r="AI204" t="n">
+        <v>41.75</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -25653,6 +26257,9 @@
       <c r="AH205" t="n">
         <v>1234668560</v>
       </c>
+      <c r="AI205" t="n">
+        <v>28.96</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -25777,6 +26384,9 @@
       <c r="AH206" t="n">
         <v>4984721250</v>
       </c>
+      <c r="AI206" t="n">
+        <v>25.8</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -25901,6 +26511,9 @@
       <c r="AH207" t="n">
         <v>1335569375</v>
       </c>
+      <c r="AI207" t="n">
+        <v>40.08</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -26025,6 +26638,9 @@
       <c r="AH208" t="n">
         <v>1510556062.5</v>
       </c>
+      <c r="AI208" t="n">
+        <v>50.85</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -26149,6 +26765,9 @@
       <c r="AH209" t="n">
         <v>1459046435</v>
       </c>
+      <c r="AI209" t="n">
+        <v>41.05</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -26273,6 +26892,9 @@
       <c r="AH210" t="n">
         <v>3948127200</v>
       </c>
+      <c r="AI210" t="n">
+        <v>44.46</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -26397,6 +27019,9 @@
       <c r="AH211" t="n">
         <v>419375955</v>
       </c>
+      <c r="AI211" t="n">
+        <v>58.22</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -26521,6 +27146,9 @@
       <c r="AH212" t="n">
         <v>797948574.5</v>
       </c>
+      <c r="AI212" t="n">
+        <v>39.41</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -26645,6 +27273,9 @@
       <c r="AH213" t="n">
         <v>983545800</v>
       </c>
+      <c r="AI213" t="n">
+        <v>24.41</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -26769,6 +27400,9 @@
       <c r="AH214" t="n">
         <v>5836779050</v>
       </c>
+      <c r="AI214" t="n">
+        <v>40.82</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -26893,6 +27527,9 @@
       <c r="AH215" t="n">
         <v>1577362342.5</v>
       </c>
+      <c r="AI215" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -27016,6 +27653,9 @@
       </c>
       <c r="AH216" t="n">
         <v>3861110500</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>40.79</v>
       </c>
     </row>
     <row r="217">
@@ -27121,6 +27761,9 @@
       <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="inlineStr"/>
       <c r="AH217" t="inlineStr"/>
+      <c r="AI217" t="n">
+        <v>53.68</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
